--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Sr Associate Data Analytics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Associate Data Analytics</t>
+          <t>Backend Engineer - AI Gateway</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Cinter Networks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -775,41 +775,6 @@
         </is>
       </c>
       <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Backend Engineer - AI Gateway</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Cinter Networks</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
         </is>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Development Engineer - US Federal</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>RoadSync</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b50b0aef4d49b0</t>
+          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Associate Software Development Engineer - US Federal</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Zookeeper, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc557eea54e41a1</t>
+          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
+          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
         </is>
       </c>
     </row>
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
+          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Senior AI/ML Platform Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Backend Engineer - AI Gateway</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RoadSync</t>
+          <t>Cinter Networks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,112 +671,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
+          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer, GovCloud</t>
+          <t>Sr Associate Data Analytics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sr Associate Data Analytics</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Amgen</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Backend Engineer - AI Gateway</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Cinter Networks</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RoadSync</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
+          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
+          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
         </is>
       </c>
     </row>
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
+          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>RoadSync</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
+          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Backend Engineer - AI Gateway</t>
+          <t>Sr Associate Data Analytics</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cinter Networks</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Associate Data Analytics</t>
+          <t>Backend Engineer - AI Gateway</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Cinter Networks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
+          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Associate Data Analytics</t>
+          <t>Backend Engineer - AI Gateway</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Cinter Networks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
+          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Backend Engineer - AI Gateway</t>
+          <t>Sr Associate Data Analytics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cinter Networks</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,52 +608,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer, GovCloud</t>
+          <t>Backend Engineer - AI Gateway</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Medallia</t>
+          <t>Cinter Networks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
+          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Backend Engineer - AI Gateway</t>
+          <t>Sr Associate Data Analytics</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cinter Networks</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -670,41 +670,6 @@
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sr Associate Data Analytics</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Amgen</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
         </is>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>RoadSync</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
+          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
+          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
         </is>
       </c>
     </row>
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
+          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RoadSync</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
+          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backend Engineer - AI Gateway</t>
+          <t>Sr Associate Data Analytics</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cinter Networks</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Associate Data Analytics</t>
+          <t>Backend Engineer - AI Gateway</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Cinter Networks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
+          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, ECS, RDS, GCP, BigQuery, Scala, NoSQL</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
+          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
         </is>
       </c>
     </row>
@@ -566,42 +566,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
+          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Backend Engineer - AI Gateway</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Cinter Networks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
+          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
         </is>
       </c>
     </row>
@@ -637,41 +637,6 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Backend Engineer - AI Gateway</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Cinter Networks</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Backend Engineer - AI Gateway</t>
+          <t>Sr Associate Data Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cinter Networks</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Associate Data Analytics</t>
+          <t>Backend Engineer - AI Gateway</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Cinter Networks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
+          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,140 +503,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7917c01121d24b96</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Sr Associate Data Analytics</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a758504314944c77</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sr Associate Data Analytics</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Amgen</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Backend Engineer - AI Gateway</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cinter Networks</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,33 +538,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Senior Backend Engineer (Remote, US)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Openly</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Sr Associate Data Analytics</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Amgen</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Tampa, FL, US USA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>11.1</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
         </is>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,33 +573,103 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Backend / Platform Developer Consultant (Temporal &amp; Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>inVeritaSoft</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Kafka, Kafka Connect, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cb9f3f7a196c2e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Billtrust</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01c9c35a4ddbdfbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Sr Associate Data Analytics</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Amgen</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Tampa, FL, US USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D7" t="n">
         <v>11.1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
         </is>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Python and React Cloud Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RoadSync</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.2</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, YARN, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
+          <t>https://www.indeed.com/viewjob?jk=04cf2cecb49ff19b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4fa506997c9d91</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Remote, US)</t>
+          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
+          <t>https://www.indeed.com/viewjob?jk=e97a7a884716018a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Backend / Platform Developer Consultant (Temporal &amp; Kubernetes)</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>inVeritaSoft</t>
+          <t>RoadSync</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb9f3f7a196c2e0</t>
+          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,40 +636,145 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01c9c35a4ddbdfbb</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Senior Backend Engineer (Remote, US)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openly</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Backend / Platform Developer Consultant (Temporal &amp; Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>inVeritaSoft</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Kafka, Kafka Connect, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cb9f3f7a196c2e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior.Net Full-Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Sr Associate Data Analytics</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Amgen</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Tampa, FL, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D10" t="n">
         <v>11.1</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
         </is>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Remote, US)</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Backend / Platform Developer Consultant (Temporal &amp; Kubernetes)</t>
+          <t>Senior Backend Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>inVeritaSoft</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb9f3f7a196c2e0</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Backend / Platform Developer Consultant (Temporal &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>inVeritaSoft</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb9f3f7a196c2e0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Associate Data Analytics</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,15 +766,50 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sr Associate Data Analytics</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
         </is>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RoadSync</t>
+          <t>Associated Materials</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cuyahoga Falls, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
+          <t>https://www.indeed.com/viewjob?jk=df0fa58d13ff3c9a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Remote, US)</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Backend / Platform Developer Consultant (Temporal &amp; Kubernetes)</t>
+          <t>Senior Backend Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>inVeritaSoft</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb9f3f7a196c2e0</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Backend / Platform Developer Consultant (Temporal &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>inVeritaSoft</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb9f3f7a196c2e0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Associate Data Analytics</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,87 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sr Associate Data Analytics</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Azure Databricks/Data Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>signitives IT Solutions</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,60 +573,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Associated Materials</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cuyahoga Falls, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df0fa58d13ff3c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Remote, US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Associated Materials</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cuyahoga Falls, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
+          <t>https://www.indeed.com/viewjob?jk=df0fa58d13ff3c9a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Backend / Platform Developer Consultant (Temporal &amp; Kubernetes)</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>inVeritaSoft</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb9f3f7a196c2e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,77 +811,567 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Associate Data Analytics</t>
+          <t>Solutions Architect - Data Governance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a3de99cc55670f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Senior ML/Data Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Catapult Sports</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Remote, US)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openly</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Insperity</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Kingwood, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DailyPay Inc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior.Net Full-Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sr Associate Data Analytics</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Woongjin, Inc</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FINRA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FINRA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FINRA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=580cc59935f51044</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Veeva Vault RegulatoryOne Business Analyst</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Aivanta Tech Inc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ewing, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97926cefb68003ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior React Developer with Java API &amp; Spring Boot Experience</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Leandro, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07cce364fcbc19ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>signitives IT Solutions</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D25" t="n">
         <v>10.4</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Associate Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Technical Product Owner, Data and Payment Technology</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Princess</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
+          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associated Materials</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cuyahoga Falls, OH, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df0fa58d13ff3c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Associated Materials</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cuyahoga Falls, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=df0fa58d13ff3c9a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Governance</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a3de99cc55670f</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Remote, US)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Solutions Architect - Data Governance</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a3de99cc55670f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Senior Backend Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Associate Data Analytics</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Sr Associate Data Analytics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580cc59935f51044</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Veeva Vault RegulatoryOne Business Analyst</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aivanta Tech Inc</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ewing, NJ, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97926cefb68003ff</t>
+          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior React Developer with Java API &amp; Spring Boot Experience</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cce364fcbc19ed</t>
+          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=580cc59935f51044</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Veeva Vault RegulatoryOne Business Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Aivanta Tech Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Ewing, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,40 +1336,250 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=97926cefb68003ff</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Senior React Developer with Java API &amp; Spring Boot Experience</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>San Leandro, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07cce364fcbc19ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Azure Databricks/Data Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>signitives IT Solutions</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Associate Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>X Development</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Technical Product Owner, Data and Payment Technology</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Princess</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D33" t="n">
         <v>10.4</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4fa506997c9d91</t>
+          <t>https://www.indeed.com/viewjob?jk=299ffa44541b6cb7</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97a7a884716018a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4fa506997c9d91</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
+          <t>https://www.indeed.com/viewjob?jk=e97a7a884716018a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Snowflake Developer – Python &amp; SQL Server</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Unitedone health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
+          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associated Materials</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cuyahoga Falls, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df0fa58d13ff3c9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f16c01d9addff559</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr. Software Engineer, ROR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Lambda, S3, ECS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=3a74eecfd78cc78a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Governance</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a3de99cc55670f</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Remote, US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Solutions Architect - Data Governance</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a3de99cc55670f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Associate Data Analytics</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Senior Backend Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580cc59935f51044</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Veeva Vault RegulatoryOne Business Analyst</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aivanta Tech Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ewing, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97926cefb68003ff</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior React Developer with Java API &amp; Spring Boot Experience</t>
+          <t>Sr Associate Data Analytics</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
+          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cce364fcbc19ed</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Senior React Developer with Java API &amp; Spring Boot Experience</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Leandro, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=07cce364fcbc19ed</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=580cc59935f51044</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,15 +1571,225 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Azure Databricks/Data Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>signitives IT Solutions</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Associate Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>X Development</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Technical Product Owner, Data and Payment Technology</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Princess</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Governance</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a3de99cc55670f</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Solutions Architect - Data Governance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a3de99cc55670f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Remote, US)</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Operations Scientist, Development</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Associate Data Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>S3, RDS, Databricks, Scala, Informatica PowerCenter, SQL Server, Power BI, Tableau, Git, Python</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior React Developer with Java API &amp; Spring Boot Experience</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cce364fcbc19ed</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580cc59935f51044</t>
+          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=580cc59935f51044</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Key2Source INC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,15 +1781,120 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Associate Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>X Development</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Technical Product Owner, Data and Payment Technology</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Princess</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=299ffa44541b6cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4fa506997c9d91</t>
+          <t>https://www.indeed.com/viewjob?jk=299ffa44541b6cb7</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97a7a884716018a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4fa506997c9d91</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Snowflake Developer – Python &amp; SQL Server</t>
+          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unitedone health</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
+          <t>https://www.indeed.com/viewjob?jk=e97a7a884716018a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Snowflake Developer – Python &amp; SQL Server</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>Unitedone health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
+          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
+          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Application Reliability Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16c01d9addff559</t>
+          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Application Reliability Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=f16c01d9addff559</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, ROR</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a74eecfd78cc78a</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Sr. Software Engineer, ROR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=3a74eecfd78cc78a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=176a7564b0c762a0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Governance</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a3de99cc55670f</t>
+          <t>https://www.indeed.com/viewjob?jk=777f4483805c8d79</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=d9bb3ce748cacccb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Operations Scientist, Development</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Solutions Architect - Data Governance</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a3de99cc55670f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Operations Scientist, Development</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580cc59935f51044</t>
+          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=580cc59935f51044</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Key2Source INC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=d285da9f2e0f5ed6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,15 +1886,225 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ab Initio Developer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Key2Source INC</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Associate Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>X Development</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Technical Product Owner, Data and Payment Technology</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Princess</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>

--- a/results/job_matches_2026-08-17.xlsx
+++ b/results/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176a7564b0c762a0</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777f4483805c8d79</t>
+          <t>https://www.indeed.com/viewjob?jk=176a7564b0c762a0</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9bb3ce748cacccb</t>
+          <t>https://www.indeed.com/viewjob?jk=777f4483805c8d79</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=d9bb3ce748cacccb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Analytics Engineer I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Governance</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a3de99cc55670f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Operations Scientist, Development</t>
+          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Solutions Architect - Data Governance</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a3de99cc55670f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580cc59935f51044</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d285da9f2e0f5ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Data Operations Scientist, Development</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=580cc59935f51044</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Key2Source INC</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,15 +2096,260 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NetSPI</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, GitHub Actions, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aa161d158387111</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ab Initio Developer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Key2Source INC</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Associate Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>X Development</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Technical Product Owner, Data and Payment Technology</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Princess</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>
